--- a/dados_fontes/produtos/protecao_movel.xlsx
+++ b/dados_fontes/produtos/protecao_movel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corpclarobr-my.sharepoint.com/personal/jonathan_goncalvessilva_claro_com_br/Documents/Jonathan/Spam/Canal360_Prototipo_React_V5_Gerencial/canal360-react/dados_fontes/produtos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{81A89C96-D30C-45AB-8FDE-7403966020FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6772F092-6EAC-44D3-814F-E4120FB9AFF1}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{81A89C96-D30C-45AB-8FDE-7403966020FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E1809E4-2379-4C65-A729-5D578BA18F66}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2467B81C-95B6-4F1F-A093-91CAAB638896}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2467B81C-95B6-4F1F-A093-91CAAB638896}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="110">
   <si>
     <t>DDD</t>
   </si>
@@ -360,6 +360,15 @@
   </si>
   <si>
     <t>4C7D</t>
+  </si>
+  <si>
+    <t>FP4S</t>
+  </si>
+  <si>
+    <t>EJFC</t>
+  </si>
+  <si>
+    <t>XTHG</t>
   </si>
 </sst>
 </file>
@@ -731,10 +740,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B772E08-B327-40C5-B8B9-E5DAA7213225}">
-  <dimension ref="A1:I64"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I67"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -763,7 +772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>12</v>
       </c>
@@ -780,19 +789,19 @@
         <v>12</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I2">
-        <v>0.2857142857142857</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>12</v>
       </c>
@@ -809,19 +818,19 @@
         <v>12</v>
       </c>
       <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3">
         <v>3</v>
       </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>12</v>
       </c>
@@ -838,19 +847,19 @@
         <v>12</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
       <c r="I4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>13</v>
       </c>
@@ -867,19 +876,19 @@
         <v>12</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>13</v>
       </c>
@@ -896,19 +905,19 @@
         <v>12</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.46153846153846156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>13</v>
       </c>
@@ -925,19 +934,19 @@
         <v>12</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>13</v>
       </c>
@@ -954,19 +963,19 @@
         <v>12</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>0.5714285714285714</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.45454545454545453</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>13</v>
       </c>
@@ -983,19 +992,19 @@
         <v>12</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
         <v>3</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
       </c>
       <c r="I9">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>13</v>
       </c>
@@ -1015,16 +1024,16 @@
         <v>2</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>13</v>
       </c>
@@ -1053,7 +1062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>13</v>
       </c>
@@ -1070,19 +1079,19 @@
         <v>12</v>
       </c>
       <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>7</v>
+      </c>
+      <c r="H12">
         <v>2</v>
       </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
       <c r="I12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>13</v>
       </c>
@@ -1102,16 +1111,16 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1128,53 +1137,53 @@
         <v>12</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
@@ -1186,24 +1195,24 @@
         <v>32</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
         <v>30</v>
@@ -1215,59 +1224,59 @@
         <v>32</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
         <v>32</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I18">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.54545454545454541</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s">
         <v>32</v>
@@ -1276,21 +1285,21 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
@@ -1302,53 +1311,53 @@
         <v>32</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
         <v>32</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>2</v>
       </c>
       <c r="I21">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
@@ -1360,27 +1369,27 @@
         <v>32</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
         <v>37</v>
@@ -1389,48 +1398,48 @@
         <v>32</v>
       </c>
       <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24">
         <v>0</v>
       </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23">
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E24" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>17</v>
       </c>
@@ -1447,19 +1456,19 @@
         <v>32</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>0.16666666666666666</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>17</v>
       </c>
@@ -1476,19 +1485,19 @@
         <v>32</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>17</v>
       </c>
@@ -1517,360 +1526,360 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>19</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29">
+        <v>23</v>
+      </c>
+      <c r="H29">
+        <v>19</v>
+      </c>
+      <c r="I29">
+        <v>0.17391304347826086</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30">
+        <v>15</v>
+      </c>
+      <c r="G30">
         <v>32</v>
       </c>
-      <c r="F28">
-        <v>2</v>
-      </c>
-      <c r="G28">
-        <v>4</v>
-      </c>
-      <c r="H28">
-        <v>2</v>
-      </c>
-      <c r="I28">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>18</v>
-      </c>
-      <c r="B29" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" t="s">
-        <v>58</v>
-      </c>
-      <c r="E29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>18</v>
-      </c>
-      <c r="B30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
       <c r="H30">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.46875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I31">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E32" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E33" t="s">
         <v>68</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>9</v>
       </c>
       <c r="H33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I33">
-        <v>0.22222222222222221</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E34" t="s">
         <v>68</v>
       </c>
       <c r="F34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="H34">
+        <v>3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>19</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35" t="s">
+        <v>68</v>
+      </c>
+      <c r="F35">
         <v>8</v>
       </c>
-      <c r="H34">
-        <v>4</v>
-      </c>
-      <c r="I34">
+      <c r="G35">
+        <v>13</v>
+      </c>
+      <c r="H35">
+        <v>5</v>
+      </c>
+      <c r="I35">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>19</v>
+      </c>
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" t="s">
+        <v>81</v>
+      </c>
+      <c r="E36" t="s">
+        <v>68</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36">
+        <v>9</v>
+      </c>
+      <c r="H36">
+        <v>4</v>
+      </c>
+      <c r="I36">
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>19</v>
+      </c>
+      <c r="B37" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" t="s">
+        <v>68</v>
+      </c>
+      <c r="F37">
+        <v>6</v>
+      </c>
+      <c r="G37">
+        <v>10</v>
+      </c>
+      <c r="H37">
+        <v>4</v>
+      </c>
+      <c r="I37">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>19</v>
+      </c>
+      <c r="B38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E38" t="s">
+        <v>68</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>6</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>19</v>
+      </c>
+      <c r="B39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39">
+        <v>4</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39">
         <v>0.5</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>19</v>
-      </c>
-      <c r="B35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" t="s">
-        <v>70</v>
-      </c>
-      <c r="E35" t="s">
-        <v>68</v>
-      </c>
-      <c r="F35">
-        <v>3</v>
-      </c>
-      <c r="G35">
-        <v>5</v>
-      </c>
-      <c r="H35">
-        <v>2</v>
-      </c>
-      <c r="I35">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>19</v>
-      </c>
-      <c r="B36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" t="s">
-        <v>73</v>
-      </c>
-      <c r="E36" t="s">
-        <v>68</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>19</v>
-      </c>
-      <c r="B37" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" t="s">
-        <v>76</v>
-      </c>
-      <c r="E37" t="s">
-        <v>68</v>
-      </c>
-      <c r="F37">
-        <v>2</v>
-      </c>
-      <c r="G37">
-        <v>6</v>
-      </c>
-      <c r="H37">
-        <v>4</v>
-      </c>
-      <c r="I37">
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>19</v>
-      </c>
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" t="s">
-        <v>76</v>
-      </c>
-      <c r="E38" t="s">
-        <v>68</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>2</v>
-      </c>
-      <c r="H38">
-        <v>2</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>19</v>
-      </c>
-      <c r="B39" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" t="s">
-        <v>67</v>
-      </c>
-      <c r="E39" t="s">
-        <v>68</v>
-      </c>
-      <c r="F39">
-        <v>6</v>
-      </c>
-      <c r="G39">
-        <v>9</v>
-      </c>
-      <c r="H39">
-        <v>3</v>
-      </c>
-      <c r="I39">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C40" t="s">
         <v>45</v>
@@ -1882,30 +1891,30 @@
         <v>68</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.42857142857142855</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E41" t="s">
         <v>68</v>
@@ -1914,21 +1923,21 @@
         <v>2</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
         <v>19</v>
@@ -1940,111 +1949,111 @@
         <v>68</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="D43" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E43" t="s">
         <v>68</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.91428571428571426</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E44" t="s">
         <v>68</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D45" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E45" t="s">
         <v>68</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
         <v>19</v>
@@ -2056,175 +2065,175 @@
         <v>68</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H46">
         <v>2</v>
       </c>
       <c r="I46">
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="D47" t="s">
+        <v>76</v>
+      </c>
+      <c r="E47" t="s">
+        <v>68</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47">
+        <v>11</v>
+      </c>
+      <c r="H47">
+        <v>7</v>
+      </c>
+      <c r="I47">
+        <v>0.36363636363636365</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>19</v>
+      </c>
+      <c r="B48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" t="s">
+        <v>68</v>
+      </c>
+      <c r="F48">
+        <v>4</v>
+      </c>
+      <c r="G48">
+        <v>13</v>
+      </c>
+      <c r="H48">
+        <v>9</v>
+      </c>
+      <c r="I48">
+        <v>0.30769230769230771</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" t="s">
+        <v>78</v>
+      </c>
+      <c r="D49" t="s">
+        <v>76</v>
+      </c>
+      <c r="E49" t="s">
+        <v>68</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>4</v>
+      </c>
+      <c r="H49">
+        <v>4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>19</v>
+      </c>
+      <c r="B50" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" t="s">
+        <v>68</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>5</v>
+      </c>
+      <c r="H50">
+        <v>4</v>
+      </c>
+      <c r="I50">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>19</v>
+      </c>
+      <c r="B51" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" t="s">
         <v>67</v>
       </c>
-      <c r="E47" t="s">
-        <v>68</v>
-      </c>
-      <c r="F47">
+      <c r="E51" t="s">
+        <v>68</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
         <v>5</v>
       </c>
-      <c r="G47">
-        <v>6</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>19</v>
-      </c>
-      <c r="B48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" t="s">
-        <v>73</v>
-      </c>
-      <c r="E48" t="s">
-        <v>68</v>
-      </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="G48">
-        <v>2</v>
-      </c>
-      <c r="H48">
-        <v>1</v>
-      </c>
-      <c r="I48">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>19</v>
-      </c>
-      <c r="B49" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="H51">
+        <v>5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>19</v>
+      </c>
+      <c r="B52" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" t="s">
         <v>67</v>
-      </c>
-      <c r="E49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49">
-        <v>3</v>
-      </c>
-      <c r="H49">
-        <v>2</v>
-      </c>
-      <c r="I49">
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>19</v>
-      </c>
-      <c r="B50" t="s">
-        <v>92</v>
-      </c>
-      <c r="C50" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" t="s">
-        <v>73</v>
-      </c>
-      <c r="E50" t="s">
-        <v>68</v>
-      </c>
-      <c r="F50">
-        <v>3</v>
-      </c>
-      <c r="G50">
-        <v>4</v>
-      </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>19</v>
-      </c>
-      <c r="B51" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" t="s">
-        <v>75</v>
-      </c>
-      <c r="D51" t="s">
-        <v>76</v>
-      </c>
-      <c r="E51" t="s">
-        <v>68</v>
-      </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51">
-        <v>4</v>
-      </c>
-      <c r="H51">
-        <v>3</v>
-      </c>
-      <c r="I51">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>19</v>
-      </c>
-      <c r="B52" t="s">
-        <v>94</v>
-      </c>
-      <c r="C52" t="s">
-        <v>78</v>
-      </c>
-      <c r="D52" t="s">
-        <v>76</v>
       </c>
       <c r="E52" t="s">
         <v>68</v>
@@ -2233,24 +2242,24 @@
         <v>2</v>
       </c>
       <c r="G52">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H52">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>0.2857142857142857</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>19</v>
       </c>
       <c r="B53" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D53" t="s">
         <v>76</v>
@@ -2259,88 +2268,88 @@
         <v>68</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.88888888888888884</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>19</v>
       </c>
       <c r="B54" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="D54" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E54" t="s">
         <v>68</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.76923076923076927</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="D55" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E55" t="s">
         <v>68</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.23076923076923078</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>19</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C56" t="s">
         <v>19</v>
       </c>
       <c r="D56" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E56" t="s">
         <v>68</v>
@@ -2349,85 +2358,85 @@
         <v>2</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>19</v>
       </c>
       <c r="B57" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C57" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="D57" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E57" t="s">
         <v>68</v>
       </c>
       <c r="F57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G57">
         <v>6</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I57">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>19</v>
       </c>
       <c r="B58" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C58" t="s">
         <v>19</v>
       </c>
       <c r="D58" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E58" t="s">
         <v>68</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H58">
         <v>2</v>
       </c>
       <c r="I58">
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C59" t="s">
         <v>19</v>
       </c>
       <c r="D59" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E59" t="s">
         <v>68</v>
@@ -2436,158 +2445,245 @@
         <v>1</v>
       </c>
       <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>19</v>
+      </c>
+      <c r="B60" t="s">
+        <v>106</v>
+      </c>
+      <c r="C60" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" t="s">
+        <v>68</v>
+      </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+      <c r="G60">
+        <v>4</v>
+      </c>
+      <c r="H60">
+        <v>2</v>
+      </c>
+      <c r="I60">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>19</v>
+      </c>
+      <c r="B61" t="s">
+        <v>108</v>
+      </c>
+      <c r="C61" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" t="s">
+        <v>83</v>
+      </c>
+      <c r="E61" t="s">
+        <v>68</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>44</v>
+      </c>
+      <c r="C62" t="s">
+        <v>45</v>
+      </c>
+      <c r="D62" t="s">
+        <v>46</v>
+      </c>
+      <c r="E62" t="s">
+        <v>47</v>
+      </c>
+      <c r="F62">
         <v>3</v>
       </c>
-      <c r="H59">
+      <c r="G62">
+        <v>4</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E63" t="s">
+        <v>47</v>
+      </c>
+      <c r="F63">
         <v>2</v>
       </c>
-      <c r="I59">
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>19</v>
-      </c>
-      <c r="B60" t="s">
-        <v>102</v>
-      </c>
-      <c r="C60" t="s">
-        <v>19</v>
-      </c>
-      <c r="D60" t="s">
-        <v>70</v>
-      </c>
-      <c r="E60" t="s">
-        <v>68</v>
-      </c>
-      <c r="F60">
+      <c r="G63">
+        <v>4</v>
+      </c>
+      <c r="H63">
+        <v>2</v>
+      </c>
+      <c r="I63">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>18</v>
+      </c>
+      <c r="B64" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F64">
+        <v>4</v>
+      </c>
+      <c r="G64">
+        <v>9</v>
+      </c>
+      <c r="H64">
+        <v>5</v>
+      </c>
+      <c r="I64">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>18</v>
+      </c>
+      <c r="B65" t="s">
+        <v>59</v>
+      </c>
+      <c r="C65" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" t="s">
+        <v>32</v>
+      </c>
+      <c r="F65">
         <v>0</v>
       </c>
-      <c r="G60">
-        <v>3</v>
-      </c>
-      <c r="H60">
-        <v>3</v>
-      </c>
-      <c r="I60">
+      <c r="G65">
+        <v>2</v>
+      </c>
+      <c r="H65">
+        <v>2</v>
+      </c>
+      <c r="I65">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>19</v>
-      </c>
-      <c r="B61" t="s">
-        <v>103</v>
-      </c>
-      <c r="C61" t="s">
-        <v>19</v>
-      </c>
-      <c r="D61" t="s">
-        <v>73</v>
-      </c>
-      <c r="E61" t="s">
-        <v>68</v>
-      </c>
-      <c r="F61">
-        <v>3</v>
-      </c>
-      <c r="G61">
-        <v>4</v>
-      </c>
-      <c r="H61">
-        <v>1</v>
-      </c>
-      <c r="I61">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>19</v>
-      </c>
-      <c r="B62" t="s">
-        <v>104</v>
-      </c>
-      <c r="C62" t="s">
-        <v>19</v>
-      </c>
-      <c r="D62" t="s">
-        <v>83</v>
-      </c>
-      <c r="E62" t="s">
-        <v>68</v>
-      </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
-      <c r="G62">
-        <v>1</v>
-      </c>
-      <c r="H62">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>18</v>
+      </c>
+      <c r="B66" t="s">
+        <v>60</v>
+      </c>
+      <c r="C66" t="s">
+        <v>57</v>
+      </c>
+      <c r="D66" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" t="s">
+        <v>32</v>
+      </c>
+      <c r="F66">
         <v>0</v>
       </c>
-      <c r="I62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>19</v>
-      </c>
-      <c r="B63" t="s">
-        <v>105</v>
-      </c>
-      <c r="C63" t="s">
-        <v>19</v>
-      </c>
-      <c r="D63" t="s">
-        <v>83</v>
-      </c>
-      <c r="E63" t="s">
-        <v>68</v>
-      </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-      <c r="G63">
-        <v>1</v>
-      </c>
-      <c r="H63">
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
         <v>0</v>
       </c>
-      <c r="I63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>19</v>
-      </c>
-      <c r="B64" t="s">
-        <v>106</v>
-      </c>
-      <c r="C64" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" t="s">
-        <v>73</v>
-      </c>
-      <c r="E64" t="s">
-        <v>68</v>
-      </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
-      <c r="G64">
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>18</v>
+      </c>
+      <c r="B67" t="s">
+        <v>61</v>
+      </c>
+      <c r="C67" t="s">
+        <v>57</v>
+      </c>
+      <c r="D67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E67" t="s">
+        <v>32</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
         <v>2</v>
       </c>
-      <c r="H64">
-        <v>2</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
